--- a/Tarifas Quebrada Verde 2026 - 2027.xlsx
+++ b/Tarifas Quebrada Verde 2026 - 2027.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mcuadradof/Desktop/EQUIPAMIENTO CABAÑAS/TARIFAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrea\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15ACB982-81DB-8B45-B500-40A62217E2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACD6698-B19F-4C64-8E58-A0DD4E42D906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28300" windowHeight="17360" xr2:uid="{4DB7E3E0-5DA8-3B4A-B25E-A6A363520D56}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4DB7E3E0-5DA8-3B4A-B25E-A6A363520D56}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -35,34 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>CABAÑA</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>TM</t>
-  </si>
-  <si>
-    <t>TA</t>
-  </si>
-  <si>
-    <t>ARRAYAN (6 pax)</t>
-  </si>
-  <si>
-    <t>21/04 - 19/06</t>
-  </si>
-  <si>
-    <t>17/03 - 20/04</t>
-  </si>
-  <si>
-    <t>12/12 - 16/03</t>
-  </si>
-  <si>
-    <t>20/06 -  11/12</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>*Valores por noche.</t>
   </si>
@@ -70,22 +43,37 @@
     <t>**Precios y Temporadas pueden estar sujetos a cambios.</t>
   </si>
   <si>
-    <t xml:space="preserve">***Minimo Estadia 2 noches.  </t>
-  </si>
-  <si>
-    <t>****Estadias por 1 noche tiene 20% de recargo. En  TA no se acepta estadia por 1 noche.</t>
-  </si>
-  <si>
     <t>TARIFAS 2026 - 2027</t>
   </si>
   <si>
-    <t>MELI/COIHUE (2/4 pax)</t>
-  </si>
-  <si>
-    <t>ULMO (2/4 pax)</t>
-  </si>
-  <si>
-    <t>ALERCE/CANELO (5/6 pax)</t>
+    <t>Capacidad (pp)</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>ARRAYAN</t>
+  </si>
+  <si>
+    <t>MELI/COIHUE</t>
+  </si>
+  <si>
+    <t>ULMO</t>
+  </si>
+  <si>
+    <t>ALERCE/CANELO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">***Mínimo Estadia 2 noches.  </t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Cabaña</t>
   </si>
 </sst>
 </file>
@@ -93,7 +81,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -139,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -148,12 +136,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -173,9 +166,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -213,7 +206,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -319,7 +312,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -461,7 +454,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -472,193 +465,140 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.1640625" customWidth="1"/>
-    <col min="2" max="2" width="18.1640625" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="1" max="1" width="19.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4">
+        <v>280000</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6">
+      <c r="C5" s="4">
         <v>170000</v>
       </c>
-      <c r="C4" s="6">
-        <v>190000</v>
-      </c>
-      <c r="D4" s="6">
-        <v>280000</v>
-      </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="6">
-        <v>110000</v>
-      </c>
-      <c r="C5" s="6">
-        <v>120000</v>
-      </c>
-      <c r="D5" s="6">
-        <v>170000</v>
-      </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="6">
-        <v>120000</v>
-      </c>
-      <c r="C6" s="6">
-        <v>135000</v>
-      </c>
-      <c r="D6" s="6">
+    <row r="6" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4">
         <v>185000</v>
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
-        <v>150000</v>
-      </c>
-      <c r="C7" s="6">
-        <v>170000</v>
-      </c>
-      <c r="D7" s="6">
+    <row r="7" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4">
         <v>250000</v>
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" ht="21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="21" x14ac:dyDescent="0.4">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="1"/>
+    <row r="9" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
+    <row r="11" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" ht="21" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="1"/>
+    <row r="12" spans="1:5" ht="21" x14ac:dyDescent="0.4">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="0" verticalDpi="0"/>

--- a/Tarifas Quebrada Verde 2026 - 2027.xlsx
+++ b/Tarifas Quebrada Verde 2026 - 2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrea\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACD6698-B19F-4C64-8E58-A0DD4E42D906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{723ED08E-8297-4B2D-B55B-7317239AD020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4DB7E3E0-5DA8-3B4A-B25E-A6A363520D56}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>*Valores por noche.</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Cabaña</t>
+  </si>
+  <si>
+    <t>****No incluye alimentación ni aseo diario.</t>
   </si>
 </sst>
 </file>
@@ -83,16 +86,9 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,9 +98,35 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Avenir Next LT Pro"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Avenir Next LT Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Avenir Next LT Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Avenir Next LT Pro"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Avenir Next LT Pro"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,27 +149,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,128 +492,131 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="1" max="1" width="23.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="11.19921875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>6</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="7">
         <v>280000</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="7">
         <v>170000</v>
       </c>
-      <c r="E5" s="1"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="7">
         <v>185000</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="7">
         <v>250000</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A9" s="7" t="s">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A10" s="7" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="7" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9"/>
+    </row>
+    <row r="12" spans="1:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">
